--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1841</v>
+        <v>2577</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1517</v>
+        <v>2090</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>932</v>
+        <v>1283</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>218</v>
+        <v>298</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>285</v>
+        <v>401</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>186</v>
+        <v>257</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>230</v>
+        <v>314</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>201</v>
+        <v>281</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>239</v>
+        <v>322</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,39 +1033,39 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>231</v>
+        <v>119</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,39 +1141,39 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>103</v>
+        <v>274</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>11</v>
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="H24" s="12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="F25" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K25" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L25" s="12" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K26" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="M26" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L26" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G27" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="I27" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>35</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="G31" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H31" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="K31" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,39 +2005,39 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>2</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>1</v>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K36" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,39 +2221,39 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G37" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2282,25 +2282,25 @@
         <v>6</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>23</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>314</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1082802547770701</v>
+        <v>34</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>228</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.03947368421052631</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>186</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.09677419354838709</v>
+        <v>18</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>322</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.03105590062111801</v>
+        <v>10</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>119</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.5966386554621849</v>
+        <v>71</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>236</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.0423728813559322</v>
+        <v>10</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>302</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.04304635761589404</v>
+        <v>13</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>162</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.1851851851851852</v>
+        <v>30</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>173</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.138728323699422</v>
+        <v>24</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>169</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0650887573964497</v>
+        <v>11</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>198</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.04040404040404041</v>
+        <v>8</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>63</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.4126984126984127</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>78</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.05128205128205128</v>
+        <v>4</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>159</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1006289308176101</v>
+        <v>16</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>92</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.108695652173913</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>155</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.08387096774193549</v>
+        <v>13</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>57</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.3859649122807017</v>
+        <v>22</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>40</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.65</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>67</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.07462686567164178</v>
+        <v>5</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>17</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.1764705882352941</v>
+        <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>139</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.04316546762589928</v>
+        <v>6</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>78</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.2564102564102564</v>
+        <v>20</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>159</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.0440251572327044</v>
+        <v>7</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>14</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>112</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.08035714285714286</v>
+        <v>9</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2577</v>
+        <v>2730</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2090</v>
+        <v>2218</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1283</v>
+        <v>1386</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>46</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>9</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>18</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>66</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J16" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="K16" s="12" t="n">
-        <v>40</v>
-      </c>
       <c r="L16" s="12" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>44</v>
@@ -1220,7 +1220,7 @@
         <v>29</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>30</v>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J19" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L19" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="M19" s="12" t="n">
         <v>28</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>24</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>26</v>
@@ -1328,10 +1328,10 @@
         <v>28</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>63</v>
+        <v>207</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,35 +1523,35 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>10</v>
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>17</v>
@@ -1652,10 +1652,10 @@
         <v>9</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,39 +1735,39 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1793,35 +1793,35 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1847,47 +1847,47 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1901,47 +1901,47 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,35 +2005,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2063,25 +2063,25 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>14</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
         <v>35</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>3</v>
@@ -2138,7 +2138,7 @@
         <v>4</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>9</v>
@@ -2171,28 +2171,28 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
@@ -2225,19 +2225,19 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="G37" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>6</v>
@@ -2246,14 +2246,14 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2282,13 +2282,13 @@
         <v>6</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>23</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>6</v>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -2322,11 +2322,7 @@
           <t>NOVARA</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
           <t>BIANCHI ENRICO</t>
@@ -2376,11 +2372,7 @@
           <t>MILANO</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>RECCHIA ALESSANDRO</t>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2730</v>
+        <v>2910</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2218</v>
+        <v>2350</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1386</v>
+        <v>1508</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="G11" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>284</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H11" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>268</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>115</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>9</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>30</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="G17" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="K17" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H17" s="12" t="n">
-        <v>172</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="L17" s="12" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>30</v>
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>12</v>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>68</v>
-      </c>
       <c r="J21" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>8</v>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>170</v>
+        <v>89</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,35 +1523,35 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J24" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K24" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K24" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L24" s="12" t="n">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>14</v>
@@ -1598,7 +1598,7 @@
         <v>17</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>10</v>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G27" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="M27" s="12" t="n">
         <v>29</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>27</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>3</v>
@@ -1901,47 +1901,47 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>37</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="J32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K32" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>145</v>
-      </c>
       <c r="M32" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F34" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L34" s="12" t="n">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2120,13 +2120,13 @@
         <v>35</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>31</v>
@@ -2138,10 +2138,10 @@
         <v>4</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2171,35 +2171,35 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2225,19 +2225,19 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>6</v>
@@ -2246,14 +2246,14 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2282,13 +2282,13 @@
         <v>6</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>23</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>6</v>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -2382,13 +2382,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2910</v>
+        <v>3095</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2350</v>
+        <v>2499</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1508</v>
+        <v>1613</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="J14" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="K14" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="K14" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="L14" s="12" t="n">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>15</v>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G15" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="H15" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="I15" s="12" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="G17" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>194</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>137</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K17" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H17" s="12" t="n">
-        <v>187</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>32</v>
-      </c>
       <c r="L17" s="12" t="n">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K18" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>198</v>
+      </c>
+      <c r="M18" s="12" t="n">
         <v>31</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>30</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>12</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>69</v>
+        <v>233</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="H22" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K22" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="L22" s="12" t="n">
-        <v>224</v>
+        <v>74</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,47 +1523,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="G26" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H26" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="K26" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H27" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="L27" s="12" t="n">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F28" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="J28" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1793,31 +1793,31 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1847,47 +1847,47 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>50</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>178</v>
+        <v>16</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>15</v>
+        <v>188</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2009,28 +2009,28 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>72</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>6</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>13</v>
@@ -2075,16 +2075,16 @@
         <v>3</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>20</v>
@@ -2120,7 +2120,7 @@
         <v>35</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>3</v>
@@ -2138,7 +2138,7 @@
         <v>4</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>12</v>
@@ -2171,35 +2171,35 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2225,19 +2225,19 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>6</v>
@@ -2246,14 +2246,14 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2282,13 +2282,13 @@
         <v>6</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>23</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>6</v>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3095</v>
+        <v>3322</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2499</v>
+        <v>2693</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1613</v>
+        <v>1764</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H12" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>209</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>193</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>65</v>
-      </c>
       <c r="K12" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>326</v>
+        <v>361</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G15" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="H15" s="12" t="n">
-        <v>39</v>
-      </c>
       <c r="I15" s="12" t="n">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>47</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>24</v>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>37</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>40</v>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1415,47 +1415,47 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L22" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>103</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>74</v>
-      </c>
       <c r="M22" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,39 +1465,39 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L25" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>184</v>
-      </c>
       <c r="M25" s="12" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,39 +1627,39 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>20</v>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H28" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="K28" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,22 +1793,22 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>1</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1847,35 +1847,35 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1901,28 +1901,28 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>1</v>
@@ -1955,19 +1955,19 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>25</v>
@@ -1976,14 +1976,14 @@
         <v>12</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2009,31 +2009,31 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>13</v>
@@ -2084,14 +2084,14 @@
         <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>20</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
         <v>35</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>3</v>
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
@@ -2192,14 +2192,14 @@
         <v>2</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2228,13 +2228,13 @@
         <v>26</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>24</v>
@@ -2246,14 +2246,14 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2282,13 +2282,13 @@
         <v>6</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>23</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>6</v>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N40" headerRowCount="1">
-  <autoFilter ref="A10:N40"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O40" headerRowCount="1">
+  <autoFilter ref="A10:O40"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA ROMA ANGOLO VIA IMOLA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>382</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>543</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>333</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>420</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MARIO ALBINO BONICALZA 127</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>437</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>209</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>278</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS VARESINA KM 13+770</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>251</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE L. CADORNA 60</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>361</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>195</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>430</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA ROMA 157</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>222</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>192</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>187</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS33KM24+86 - SEMPIONE</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>332</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>297</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA S.VITO SILVESTRO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>337</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA RISORGIMENTO 12</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>236</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GIUSEPPE  MAZZINI SNC</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>237</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>LORENTEGGIO 0239</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MONTEROSA 6</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>243</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 233 KM 20+110</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>188</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>195</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>167</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE MARCONI 64</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>58</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L31" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SP 31 KM 12+45</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>195</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.P 59 KM 6.500 VIGEVANESE</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>164</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>C.SO VERCELLI, 138</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>55</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I35" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>25</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>15</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I37" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>DUE GIUGNO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2322,26 +2478,28 @@
           <t>NOVARA</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>CORSO RISORGIMENTO</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>0</v>
@@ -2355,7 +2513,10 @@
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2372,26 +2533,28 @@
           <t>MILANO</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>VIA FORZE ARMATE 34</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="I40" s="12" t="n">
         <v>17</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
@@ -2405,7 +2568,10 @@
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3322</v>
+        <v>3519</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2693</v>
+        <v>2846</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1764</v>
+        <v>1885</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>15</v>
@@ -960,16 +960,16 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>206</v>
@@ -978,13 +978,13 @@
         <v>74</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>24</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>43</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>31</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA MONTEROSA 6</t>
+          <t>SS 233 KM 20+110</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>VIA MONTEROSA 6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>137</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>243</v>
-      </c>
       <c r="N23" s="12" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SS 233 KM 20+110</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H26" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I26" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="J26" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="J27" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="M27" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>195</v>
-      </c>
       <c r="N27" s="12" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>117</v>
+        <v>24</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>C.SO TRIESTE, 54B</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,39 +1900,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,22 +2022,22 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>2</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2081,35 +2081,35 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>18</v>
@@ -2161,10 +2161,10 @@
         <v>16</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2202,13 +2202,13 @@
         <v>50</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>49</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>3</v>
@@ -2270,7 +2270,7 @@
         <v>3</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>12</v>
@@ -2279,10 +2279,10 @@
         <v>4</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0</v>
@@ -2329,23 +2329,23 @@
         <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G37" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J37" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H37" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="K37" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3519</v>
+        <v>3704</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2846</v>
+        <v>2988</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1885</v>
+        <v>2009</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>575</v>
+        <v>626</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,52 +1078,52 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02261</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE OLONA</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SS33KM24+86 - SEMPIONE</t>
+          <t>VIA S.VITO SILVESTRO</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>339</v>
+        <v>382</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>306</v>
+        <v>451</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>24</v>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>02261</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>SAN VITTORE OLONA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA S.VITO SILVESTRO</t>
+          <t>SS33KM24+86 - SEMPIONE</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,35 +1192,35 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>219</v>
+        <v>149</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>426</v>
+        <v>322</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>LORENTEGGIO 0239</t>
+          <t>SS 233 KM 20+110</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>55</v>
-      </c>
       <c r="J21" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>220</v>
+        <v>121</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SS 233 KM 20+110</t>
+          <t>LORENTEGGIO 0239</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>111</v>
+        <v>233</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>26</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>9</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>10</v>
@@ -1727,35 +1727,35 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>29</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>C.SO TRIESTE, 54B</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>24</v>
+        <v>215</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,39 +1900,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>206</v>
+        <v>25</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2143,13 +2143,13 @@
         <v>59</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>79</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>49</v>
@@ -2161,7 +2161,7 @@
         <v>16</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>8</v>
@@ -2202,13 +2202,13 @@
         <v>50</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>49</v>
@@ -2220,10 +2220,10 @@
         <v>0</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CORSO EUROPA</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
         <v>36</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,39 +2313,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>7</v>
@@ -2397,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2438,13 +2438,13 @@
         <v>6</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>6</v>
@@ -2456,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3704</v>
+        <v>3966</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2988</v>
+        <v>3201</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2009</v>
+        <v>2180</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>626</v>
+        <v>697</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>462</v>
+        <v>491</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02308</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIALE L. CADORNA 60</t>
+          <t>VIA ROMA 157</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,56 +1015,56 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>396</v>
+        <v>240</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>477</v>
+        <v>173</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>02308</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 157</t>
+          <t>VIALE L. CADORNA 60</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,39 +1074,39 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>214</v>
+        <v>420</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>162</v>
+        <v>500</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>24</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>39</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,52 +1373,52 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SS 233 KM 20+110</t>
+          <t>LORENTEGGIO 0239</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>121</v>
+        <v>247</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>LORENTEGGIO 0239</t>
+          <t>SS 233 KM 20+110</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>233</v>
+        <v>126</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>80</v>
@@ -1568,17 +1568,17 @@
         <v>35</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>9</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>10</v>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>PACE</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L26" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>233</v>
+      </c>
+      <c r="N26" s="12" t="n">
         <v>26</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>215</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>25</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>29</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>60</v>
+        <v>234</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>215</v>
+        <v>69</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE MARCONI 64</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J30" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>75</v>
-      </c>
       <c r="N30" s="12" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA M. T. ROSSI  17/3</t>
+          <t>SP 31 KM 12+45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SP 31 KM 12+45</t>
+          <t>VIALE MARCONI 64</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,39 +2077,39 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L33" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="M33" s="12" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="G34" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="H34" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>21</v>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2320,13 +2320,13 @@
         <v>36</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>32</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>7</v>
@@ -2397,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>2</v>
@@ -2438,13 +2438,13 @@
         <v>6</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>6</v>
@@ -2456,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3966</v>
+        <v>4135</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3201</v>
+        <v>3338</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2180</v>
+        <v>2283</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -936,17 +936,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>GARBAGNATE MILANESE</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SS VARESINA KM 13+770</t>
+          <t>VIA ROMA 157</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,56 +956,56 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>383</v>
+        <v>244</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>298</v>
+        <v>180</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>GARBAGNATE MILANESE</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 157</t>
+          <t>SS VARESINA KM 13+770</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,39 +1015,39 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>240</v>
+        <v>403</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>173</v>
+        <v>311</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>30</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>45</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>59</v>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>61</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>29</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA MONTEROSA 6</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>104</v>
+        <v>313</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>295</v>
+        <v>142</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>VIA MONTEROSA 6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="I26" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K26" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="N26" s="12" t="n">
         <v>43</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="L26" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>233</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>26</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>PACE</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>69</v>
+        <v>248</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>C.SO TRIESTE, 54B</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
         <v>76</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA M. T. ROSSI  17/3</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>64</v>
@@ -2040,13 +2040,13 @@
         <v>29</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,35 +2081,35 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>40</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>21</v>
@@ -2258,52 +2258,52 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CORSO EUROPA</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2320,49 +2320,49 @@
         <v>36</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SS 33</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
         <v>23</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>6</v>
@@ -2456,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4135</v>
+        <v>4398</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3338</v>
+        <v>3567</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2283</v>
+        <v>2452</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>485</v>
+        <v>514</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>717</v>
+        <v>735</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>77</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>517</v>
+        <v>561</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>45</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>509</v>
+        <v>540</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>198</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>61</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>28</v>
@@ -1571,7 +1571,7 @@
         <v>39</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>10</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>142</v>
+        <v>266</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>156</v>
+        <v>228</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>245</v>
+        <v>73</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>29</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,35 +2022,35 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>21</v>
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2320,13 +2320,13 @@
         <v>36</v>
       </c>
       <c r="G36" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I36" s="12" t="n">
         <v>36</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>29</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>34</v>
@@ -2338,14 +2338,14 @@
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>3</v>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4398</v>
+        <v>4664</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3567</v>
+        <v>3784</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2452</v>
+        <v>2645</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>735</v>
+        <v>764</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>43</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K14" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="L14" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="L14" s="12" t="n">
-        <v>79</v>
-      </c>
       <c r="M14" s="12" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>561</v>
+        <v>598</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>540</v>
+        <v>582</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>31</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>101</v>
-      </c>
       <c r="K21" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>266</v>
+        <v>340</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA MONTEROSA 6</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>VIA MONTEROSA 6</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="K26" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="L26" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L26" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="M26" s="12" t="n">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>161</v>
+        <v>241</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I27" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="J27" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="J27" s="12" t="n">
-        <v>66</v>
-      </c>
       <c r="K27" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>73</v>
+        <v>161</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,22 +1904,22 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>3</v>
@@ -1963,28 +1963,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>7</v>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,35 +2081,35 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>72</v>
-      </c>
       <c r="I32" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2199,35 +2199,35 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>21</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2320,13 +2320,13 @@
         <v>36</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>34</v>
@@ -2379,13 +2379,13 @@
         <v>36</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>32</v>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4664</v>
+        <v>4909</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3784</v>
+        <v>4010</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2645</v>
+        <v>2835</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>536</v>
+        <v>575</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>764</v>
+        <v>794</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>460</v>
+        <v>496</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>43</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="K14" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="L14" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="L14" s="12" t="n">
-        <v>82</v>
-      </c>
       <c r="M14" s="12" t="n">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>598</v>
+        <v>647</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>50</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>582</v>
+        <v>617</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>58</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>00120</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>COSSATO</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSEPPE  MAZZINI SNC</t>
+          <t>VIA IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>192</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>161</v>
-      </c>
       <c r="K19" s="12" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>320</v>
+        <v>124</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>00120</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>COSSATO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA IV NOVEMBRE</t>
+          <t>VIA GIUSEPPE  MAZZINI SNC</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>88</v>
+        <v>199</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>173</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>115</v>
+        <v>336</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>340</v>
+        <v>86</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>173</v>
+        <v>218</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>78</v>
+        <v>357</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>161</v>
+        <v>297</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>PACE</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>161</v>
+        <v>248</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>279</v>
+        <v>170</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>88</v>
-      </c>
       <c r="K30" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,35 +2081,35 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2199,35 +2199,35 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>21</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G35" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="I35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="J35" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>43</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2379,13 +2379,13 @@
         <v>36</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>32</v>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O40" headerRowCount="1">
-  <autoFilter ref="A10:O40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O41" headerRowCount="1">
+  <autoFilter ref="A10:O41"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4909</v>
+        <v>5039</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4010</v>
+        <v>4112</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2835</v>
+        <v>3017</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>VIA NOVARA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>185</v>
+        <v>574</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>63</v>
+        <v>875</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>294</v>
+        <v>159</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="K24" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>294</v>
+      </c>
+      <c r="N24" s="12" t="n">
         <v>36</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>49</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>357</v>
+        <v>86</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA MONTEROSA 6</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>108</v>
+        <v>218</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>154</v>
+        <v>11</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>126</v>
+        <v>357</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>PACE</t>
+          <t>VIA MONTEROSA 6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>297</v>
+        <v>126</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>248</v>
+        <v>173</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>170</v>
+        <v>297</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA M. T. ROSSI  17/3</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>27</v>
+        <v>170</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>C.SO TRIESTE, 54B</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SP 31 KM 12+45</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="H31" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>70</v>
-      </c>
       <c r="K31" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M31" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L31" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>287</v>
-      </c>
       <c r="N31" s="12" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIALE MARCONI 64</t>
+          <t>SP 31 KM 12+45</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,20 +2077,20 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>70</v>
@@ -2099,34 +2099,34 @@
         <v>31</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>113</v>
+        <v>287</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>S.P 59 KM 6.500 VIGEVANESE</t>
+          <t>VIALE MARCONI 64</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>139</v>
+        <v>36</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>244</v>
+        <v>113</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>C.SO VERCELLI, 138</t>
+          <t>S.P 59 KM 6.500 VIGEVANESE</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="H34" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>139</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="K34" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="L34" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>104</v>
+        <v>244</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>C.SO VERCELLI, 138</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="K35" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="N35" s="12" t="n">
         <v>21</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>SS 33</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CORSO EUROPA</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2376,52 +2376,52 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="H37" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>DUE GIUGNO</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,91 +2470,95 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>00425</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>SANTHIÀ</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CORSO RISORGIMENTO</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>DUE GIUGNO</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>52247</t>
+          <t>00425</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA FORZE ARMATE 34</t>
+          <t>CORSO RISORGIMENTO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
@@ -2572,6 +2576,61 @@
         <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>52247</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>VIA FORZE ARMATE 34</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>RECCHIA ALESSANDRO</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DANESE CARLO.xlsx
@@ -684,13 +684,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5039</v>
+        <v>5064</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4112</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3017</v>
+        <v>2960</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>166</v>
@@ -854,7 +854,7 @@
         <v>153</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>233</v>
@@ -863,10 +863,10 @@
         <v>83</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -877,17 +877,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>02862</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASSANO MAGNAGO</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA MARIO ALBINO BONICALZA 127</t>
+          <t>VIA ROMA 157</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -897,56 +897,56 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>577</v>
+        <v>277</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>394</v>
+        <v>207</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>02862</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>CASSANO MAGNAGO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 157</t>
+          <t>VIA MARIO ALBINO BONICALZA 127</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,39 +956,39 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>279</v>
+        <v>569</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>210</v>
+        <v>387</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1022,16 +1022,16 @@
         <v>341</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>91</v>
@@ -1040,10 +1040,10 @@
         <v>83</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>71</v>
@@ -1099,7 +1099,7 @@
         <v>75</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>39</v>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>383</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>93</v>
@@ -1158,7 +1158,7 @@
         <v>50</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>35</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>272</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>63</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>96</v>
@@ -1276,10 +1276,10 @@
         <v>47</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>00120</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>COSSATO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA IV NOVEMBRE</t>
+          <t>VIA GIUSEPPE  MAZZINI SNC</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>00120</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>COSSATO</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSEPPE  MAZZINI SNC</t>
+          <t>VIA IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>85</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>336</v>
+        <v>120</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>67</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>57</v>
@@ -1453,10 +1453,10 @@
         <v>32</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>52</v>
@@ -1512,31 +1512,31 @@
         <v>34</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>66</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA NOVARA</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>574</v>
+        <v>215</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>182</v>
+        <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>875</v>
+        <v>42</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>159</v>
+        <v>355</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>126</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>62</v>
@@ -1621,7 +1621,7 @@
         <v>63</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>43</v>
@@ -1630,7 +1630,7 @@
         <v>22</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>36</v>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>VIA NOVARA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>184</v>
+        <v>559</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>96</v>
+        <v>846</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>357</v>
+        <v>86</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>154</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>43</v>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>173</v>
@@ -1857,7 +1857,7 @@
         <v>116</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>31</v>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>62</v>
@@ -1916,7 +1916,7 @@
         <v>125</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>20</v>
@@ -1925,7 +1925,7 @@
         <v>34</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>14</v>
@@ -1966,7 +1966,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>73</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>21</v>
@@ -1984,7 +1984,7 @@
         <v>3</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>2</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>12</v>
@@ -2034,7 +2034,7 @@
         <v>8</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>39</v>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>88</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>137</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>92</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>81</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>31</v>
@@ -2102,7 +2102,7 @@
         <v>23</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>35</v>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIALE MARCONI 64</t>
+          <t>S.P 59 KM 6.500 VIGEVANESE</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>113</v>
+        <v>242</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.P 59 KM 6.500 VIGEVANESE</t>
+          <t>VIALE MARCONI 64</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,39 +2195,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>244</v>
+        <v>112</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2258,19 +2258,19 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>33</v>
@@ -2279,14 +2279,14 @@
         <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>21</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>21</v>
@@ -2338,31 +2338,31 @@
         <v>2</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SS 33</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2376,52 +2376,52 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CORSO EUROPA</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="H38" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="N38" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>15</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2500,13 +2500,13 @@
         <v>60</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>14</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
@@ -2552,13 +2552,13 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
